--- a/context_DB/SDN_context_db.xlsx
+++ b/context_DB/SDN_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,95 +761,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SD01004</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>February 2025: An educator was killed in his home by the RSF.</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Vigilante</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+          <t>SD01002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -893,22 +831,22 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Students (Sudan)</t>
+          <t>Teachers (Sudan)</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Around 25 January 2025 (as reported), RSF killed a student in an unspecified location in Sharg An Neel (location coded to locality capital Ed Babkir, Sharg An Neel, Khartoum) as he was returning from sitting for examinations in Shendi city.</t>
+          <t>On 10 February 2024, RSF abducted two teachers and killed one of them in Ombada (Um Bada, Khartoum), one of the victims was tortured. No further information.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Sharg An Neel</t>
+          <t>Um Bada</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -918,100 +856,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SD01006</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2025-05-25 ---- 2025-05-21 ---- 2025-03-05 ---- 2025-01-21 ---- 2024-09-21 ---- 2024-08-10 ---- 2024-02-10</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 2025: An educator was arrested by the RSF, then subjected to torture and deliberate starvation inside a detention centre. He was later killed despite his family having paid a ransom for his release. ---- May 2025: An education facility was used to hold 648 hostages kidnapped by the RSF, including health workers. The hostages were freed by the SAF on 21 May, although 465 were discovered in a mass grave. ---- March 2025: An education facility was struck during an RSF artillery attack. ---- January 2025: An education facility was shelled by RSF artillery, injuring an unspecified number of people. ---- September 2024: An educational facility sheltering displaced people was hit by RSF artillery bombing, killing two children. ---- August 2024: A kindergarten sheltering IDPs was hit by a suspected RSF drone strike, killing a boy.  ---- February 2024: Two educators were arrested by the RSF. One was killed and the other was tortured. </t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms ---- Artillery ---- Artillery ---- Artillery ---- Aerial Bomb: Drone ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- School: No Further Details ---- Secondary School ---- School: No Further Details ---- University ---- Pre-School ---- Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Killed ---- Killed, NoInformation</t>
-        </is>
-      </c>
+          <t>SD01003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
@@ -1020,10 +892,10 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1033,43 +905,43 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Battles ---- Strategic developments ---- Battles ---- Strategic developments</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Government regains territory ---- Disrupted weapons use ---- Armed clash ---- Other</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-) Military Intelligence Service ---- Military Forces of Sudan (2019-) ---- Rapid Support Forces</t>
+          <t>Rapid Support Forces</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Civilians (Sudan)</t>
+          <t>Civilians (Sudan)</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (South Sudan) ---- Prisoners (Sudan)</t>
+          <t>Military Forces of Sudan (2019-); Teachers (Sudan)</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>On 12 March 2024, clashes between SAF and RSF continued in Radio and TV Commission in Omdurman - Al-Mulazmin (Omdurman, Khartoum), with artillery shelling being reported. SAF regained control over the neighborhood including Radio and TV Commission buildings and Ali Abdel Fattah Students Housing. SAF destroyed many RSF vehicles and a supply crossing the River Nile and captured 120 RSF military vehicles, quantities of weapons, ammunition, and drones jamming systems. SAF captured many RSF soldiers including 14 South Sudanese militants fighting with RSF. SAF killed many RSF soldiers. SAF released the abducted civilians. Unspecified fatalities in a high intensity clash coded as 10. ---- Weapons seizure: Around 13 March 2024 (week of), SAF Military Intelligence seized an RSF ammunition warehouse at a school in Omdurman - Al-Mulazmin (Omdurman, Khartoum). ---- On 20 May 2025, clashes between SAF and RSF continued in Omdurman - Abu Rof (Omdurman, Khartoum), with RSF drone strikes targeting Khartoum University Faculty of Education building in Al Sharafia neighborhood in the area, and SAF anti-aircraft fire being reported. Casualties unknown. ---- Mass grave: Around 21 May 2025 (as reported), SAF discovered a mass grave of 465 individuals buried by RSF in the courtyard of a school in Omdurman - Al Salha (Omdurman, Khartoum) after they died of starvation and illness while being detained by RSF for 2 years. SAF also freed hundreds of RSF detainees from the school.</t>
+          <t>On 19 January 2025, RSF killed a teacher in front of her house in Al Sagai (Bahri, Khartoum) after she called for the release of her son who was abducted by RSF on an unspecified day. RSF also accused her of collaborating with SAF.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2024-03-12 ---- 2024-03-13 ---- 2025-05-20 ---- 2025-05-21</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Omdurman</t>
+          <t>Bahri</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -1079,7 +951,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SD01007</t>
+          <t>SD01004</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1101,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1135,56 +1007,100 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>March 2025: The vicinity of an education facility was hit by a drone strike.</t>
+          <t>February 2025: An educator was killed in his home by the RSF.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Vigilante</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Unidentified Armed Actor</t>
+          <t>Rapid Support Forces</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aerial Bomb: Drone</t>
+          <t>Firearms</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>School: No Further Details</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SD01</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Around 25 January 2025 (as reported), RSF killed a student in an unspecified location in Sharg An Neel (location coded to locality capital Ed Babkir, Sharg An Neel, Khartoum) as he was returning from sitting for examinations in Shendi city.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Sharg An Neel</t>
+        </is>
+      </c>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
@@ -1192,113 +1108,86 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SD02113</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">December 2024: An educational facility sheltering IDPs was hit by an RSF drone, killing an unspecified number of people and injuring 17._x000D_
-</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Vigilante</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Drone</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>SD01005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>SD01</t>
+        </is>
+      </c>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Shelling/artillery/missile attack</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>On 18 April 2024, RSF shelled artillery targeting Al Manara area in Al Jarrafa (Karrari, Khartoum). A house and school were burned. There were no casualties.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Karrari</t>
+        </is>
+      </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
@@ -1306,41 +1195,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SD02114</t>
+          <t>SD01006</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1358,108 +1247,106 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2025-02-03 ---- 2024-12-31 ---- 2024-11-25 ---- 2024-09-26 ---- 2024-09-11 ---- 2024-09-03 ---- 2024-08-26 ---- 2024-08-25 ---- 2024-08-22 ---- 2024-07-01 ---- 2024-06-27 ---- 2024-06-26 ---- 2024-06-18 ---- 2024-05-15</t>
+          <t>2025-05-25 ---- 2025-05-21 ---- 2025-03-05 ---- 2025-01-21 ---- 2024-09-21 ---- 2024-08-10 ---- 2024-02-10</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>February 2025: An educator killed by RSF. ---- December 2024: An education facility in a camp was hit by RSF artillery shelling, killing a woman and injuring an unspecified number of others. ---- November 2024: A school was damaged by SAF airstrikes. ---- September 2024: An educational facility sheltering displaced people was hit by RSF artillery. ---- September 2024: A school was hit by RSF artillery shells, killing three women and injuring four others, three of whom were taken to the military hospital._x000D_
- ---- September 2024: A secondary school was damaged when the RSF bombed residential neighbourhoods with heavy weapons. Two people died and dozens were wounded across the city. ---- August 2024: College was destroyed by RSF artillery strikes.  ---- August 2024: A college was destroyed during RSF artillery shelling. The destruction included large parts of the college, including the main hall, the laboratory and the morgue. ---- August 2024: A university was struck by the RSF shelling.  ---- July 2024: A mosque, including its Koran school and charity kitchen, were hit by RSF shelling. Of the children present in the mosque compound, nine, including an infant, were killed._x000D_
- ---- June 2024: A professor was killed inside a university by artillery shells. ---- June 2024: A university's transportation stop was bombed by the RSF, and the head of a faculty was wounded. He was transferred to a hospital, where he died during surgery to treat his injuries.  ---- June 2024: A school occupied by the RSF was shelled by the SAF, backed by Darfur Joint Forces/JSAMF during clashes between the parties. ---- May 2024: A school was hit by RSF shelling, killing and injuring an unspecified number of people.</t>
+          <t xml:space="preserve">May 2025: An educator was arrested by the RSF, then subjected to torture and deliberate starvation inside a detention centre. He was later killed despite his family having paid a ransom for his release. ---- May 2025: An education facility was used to hold 648 hostages kidnapped by the RSF, including health workers. The hostages were freed by the SAF on 21 May, although 465 were discovered in a mass grave. ---- March 2025: An education facility was struck during an RSF artillery attack. ---- January 2025: An education facility was shelled by RSF artillery, injuring an unspecified number of people. ---- September 2024: An educational facility sheltering displaced people was hit by RSF artillery bombing, killing two children. ---- August 2024: A kindergarten sheltering IDPs was hit by a suspected RSF drone strike, killing a boy.  ---- February 2024: Two educators were arrested by the RSF. One was killed and the other was tortured. </t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+          <t>Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Vigilante ---- Vigilante ---- Other ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- NSA ---- Vigilante ---- Multiple ---- Vigilante</t>
+          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Unidentified Armed Actor ---- Rapid Support Forces ---- Rapid Support Forces, Sudanese Armed Forces ---- Rapid Support Forces</t>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Firearms ---- Artillery ---- Aerial Bomb: Plane ---- Artillery ---- Artillery ---- Unspecified Explosive ---- Artillery ---- Artillery ---- Shelling ---- Shelling ---- Artillery ---- Unspecified Explosive ---- Firearms, Shelling ---- Shelling</t>
+          <t>Firearms ---- Firearms ---- Artillery ---- Artillery ---- Artillery ---- Aerial Bomb: Drone ---- Firearms</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Not Applicable ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- University ---- School: No Further Details ---- University ---- School: No Further Details ---- University ---- University ---- School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
+          <t>Not Applicable ---- School: No Further Details ---- Secondary School ---- School: No Further Details ---- University ---- Pre-School ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Killed ---- Killed, NoInformation</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>North Darfur</t>
+          <t>Khartoum</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>SD02</t>
+          <t>SD01</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Protests ---- Battles ---- Battles ---- Battles</t>
+          <t>Battles ---- Strategic developments ---- Battles ---- Strategic developments</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Armed clash ---- Armed clash ---- Armed clash</t>
+          <t>Government regains territory ---- Disrupted weapons use ---- Armed clash ---- Other</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Protesters (Sudan) ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Refugees/IDPs (Sudan); Students (Sudan); Women (Sudan) ---- Darfur Arab Militia (Sudan) ---- Darfur Arab Militia (Sudan) ---- Darfur Arab Militia (Sudan)</t>
-        </is>
-      </c>
+          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-) Military Intelligence Service ---- Military Forces of Sudan (2019-) ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-)</t>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Civilians (Sudan)</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Darfur Joint Forces/JSAMF: Joint Force of Armed Struggle Movement ---- Darfur Joint Forces/JSAMF: Joint Force of Armed Struggle Movement</t>
+          <t>Unidentified Armed Group (South Sudan) ---- Prisoners (Sudan)</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>On 2 April 2024, Union school for girls IDPs-students staged a protest in El Fasher (Al Fasher, North Darfur), demanding water, food and sanitation. ---- On 18 June 2024, clashes between RSF, backed by allied militias (described as Arab militias, coded as Darfur Arab militia), and SAF, backed by Darfur Joint Forces/JSAMF, continued in north El Fasher (Al Fasher, North Darfur), with exchange artillery shelling being reported while SAF shelled a school which SAF claimed that RSF soldiers hid in. RSF advanced from the northern front into the city and were repelled by the Joint forces. SAF ordered civilians to evict their houses and deployed forces in Bernjia, Dadnga, Al Kifah, and Al Gadi neighborhoods. 4 - 15 civilians were killed and 19 were wounded. Civilians displacement continued. ---- On 3 September 2024, SAF airstrikes targeted RSF and inflected losses on them east El Fasher (Al Fasher, North Darfur), while RSF, backed by allied Arab militias (coded as Darfur Arab militia) shelled artillery targeting Al Radef, Tembasi, Al Riyad, and IDPs shelters in Al Ithad and Ibn Sena schools in El Fasher (Al Fasher, North Darfur). 2-4 civilians were killed and tens were wounded. Unspecified RSF fatalities coded as 10. Fatalities coded as 12 (2+10). ---- On 8 September 2024, clashes between RSF, backed by allied Arab militias (coded as Darfur Arab militia), and SAF, backed by Darfur Joint Forces/JSAMF, continued in south and east El Fasher (Al Fasher, North Darfur), with SAF airstrikes targeted RSF in north, east and south of the city additionally SAF and the Joint forces ground anti-aircraft fire shot down 30 RSF fighter drones which was reported includes C4. The Joint forces regained control over Al Manhal school. Casualties unknown.</t>
+          <t>On 12 March 2024, clashes between SAF and RSF continued in Radio and TV Commission in Omdurman - Al-Mulazmin (Omdurman, Khartoum), with artillery shelling being reported. SAF regained control over the neighborhood including Radio and TV Commission buildings and Ali Abdel Fattah Students Housing. SAF destroyed many RSF vehicles and a supply crossing the River Nile and captured 120 RSF military vehicles, quantities of weapons, ammunition, and drones jamming systems. SAF captured many RSF soldiers including 14 South Sudanese militants fighting with RSF. SAF killed many RSF soldiers. SAF released the abducted civilians. Unspecified fatalities in a high intensity clash coded as 10. ---- Weapons seizure: Around 13 March 2024 (week of), SAF Military Intelligence seized an RSF ammunition warehouse at a school in Omdurman - Al-Mulazmin (Omdurman, Khartoum). ---- On 20 May 2025, clashes between SAF and RSF continued in Omdurman - Abu Rof (Omdurman, Khartoum), with RSF drone strikes targeting Khartoum University Faculty of Education building in Al Sharafia neighborhood in the area, and SAF anti-aircraft fire being reported. Casualties unknown. ---- Mass grave: Around 21 May 2025 (as reported), SAF discovered a mass grave of 465 individuals buried by RSF in the courtyard of a school in Omdurman - Al Salha (Omdurman, Khartoum) after they died of starvation and illness while being detained by RSF for 2 years. SAF also freed hundreds of RSF detainees from the school.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2024-04-02 ---- 2024-06-18 ---- 2024-09-03 ---- 2024-09-08</t>
+          <t>2024-03-12 ---- 2024-03-13 ---- 2025-05-20 ---- 2025-05-21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Al Fasher</t>
+          <t>Omdurman</t>
         </is>
       </c>
       <c r="AQ7" t="n">
@@ -1469,11 +1356,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SD02129</t>
+          <t>SD01007</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1488,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1503,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1525,12 +1412,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>February 2025: An educational facility was damaged by an SAF airstrike.</t>
+          <t>March 2025: The vicinity of an education facility was hit by a drone strike.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1540,17 +1427,17 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Sudanese Armed Forces</t>
+          <t>Unidentified Armed Actor</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aerial Bomb: Plane</t>
+          <t>Aerial Bomb: Drone</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1561,60 +1448,20 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>North Darfur</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>SD02</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Air/drone strike ---- Air/drone strike</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-)</t>
-        </is>
-      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
-        </is>
-      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>On 25 November 2024, SAF airstrikes targeted Koma (Al Fasher, North Darfur). 15 civilians were wounded. 19 houses and a school were damaged. ---- On 13 February 2025, SAF airstrikes targeted Koma (Al Fasher, North Darfur). A civilian was wounded. A school was damaged.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>2024-11-25 ---- 2025-02-13</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Melit</t>
-        </is>
-      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
@@ -1622,7 +1469,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SD03161</t>
+          <t>SD02113</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1656,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1678,12 +1525,12 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">February 2024: a secondary school was looted and destroyed by the RSF. 170 chairs, 150 stairs steps, 30 educators‚Äô desks, ten cupboards, two large water pipes, a car, doors, windows, roof material and a laboratory were taken._x000D_
+          <t xml:space="preserve">December 2024: An educational facility sheltering IDPs was hit by an RSF drone, killing an unspecified number of people and injuring 17._x000D_
 </t>
         </is>
       </c>
@@ -1704,12 +1551,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Firearms</t>
+          <t>Aerial Bomb: Drone</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Secondary School</t>
+          <t>School: No Further Details</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr"/>
@@ -1736,14 +1583,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SD03167</t>
+          <t>SD02114</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1755,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1770,13 +1617,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1788,41 +1635,43 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2024-12-17 ---- 2024-10-05 ---- 2024-08-24</t>
+          <t>2025-02-03 ---- 2024-12-31 ---- 2024-11-25 ---- 2024-09-26 ---- 2024-09-11 ---- 2024-09-03 ---- 2024-08-26 ---- 2024-08-25 ---- 2024-08-22 ---- 2024-07-01 ---- 2024-06-27 ---- 2024-06-26 ---- 2024-06-18 ---- 2024-05-15</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">December 2024: An education facility sheltering IDPs was hit by SAF airstrikes, killing nine people and injuring at least 15 other including children.  ---- October 2024: An educator was stabbed and killed by an unidentified militia. ---- As reported in August 2024: The faculties of Medicine and Health at a university were looted by the RSF. </t>
+          <t>February 2025: An educator killed by RSF. ---- December 2024: An education facility in a camp was hit by RSF artillery shelling, killing a woman and injuring an unspecified number of others. ---- November 2024: A school was damaged by SAF airstrikes. ---- September 2024: An educational facility sheltering displaced people was hit by RSF artillery. ---- September 2024: A school was hit by RSF artillery shells, killing three women and injuring four others, three of whom were taken to the military hospital._x000D_
+ ---- September 2024: A secondary school was damaged when the RSF bombed residential neighbourhoods with heavy weapons. Two people died and dozens were wounded across the city. ---- August 2024: College was destroyed by RSF artillery strikes.  ---- August 2024: A college was destroyed during RSF artillery shelling. The destruction included large parts of the college, including the main hall, the laboratory and the morgue. ---- August 2024: A university was struck by the RSF shelling.  ---- July 2024: A mosque, including its Koran school and charity kitchen, were hit by RSF shelling. Of the children present in the mosque compound, nine, including an infant, were killed._x000D_
+ ---- June 2024: A professor was killed inside a university by artillery shells. ---- June 2024: A university's transportation stop was bombed by the RSF, and the head of a faculty was wounded. He was transferred to a hospital, where he died during surgery to treat his injuries.  ---- June 2024: A school occupied by the RSF was shelled by the SAF, backed by Darfur Joint Forces/JSAMF during clashes between the parties. ---- May 2024: A school was hit by RSF shelling, killing and injuring an unspecified number of people.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building  ---- Unspecified Location ---- Education Building </t>
+          <t xml:space="preserve">Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Other ---- NSA ---- Vigilante</t>
+          <t>Vigilante ---- Vigilante ---- Other ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- NSA ---- Vigilante ---- Multiple ---- Vigilante</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Sudanese Armed Forces ---- Militia ---- Rapid Support Forces</t>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Unidentified Armed Actor ---- Rapid Support Forces ---- Rapid Support Forces, Sudanese Armed Forces ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aerial Bomb: Plane ---- Knife ---- No Information on the Weapon Used</t>
+          <t>Firearms ---- Artillery ---- Aerial Bomb: Plane ---- Artillery ---- Artillery ---- Unspecified Explosive ---- Artillery ---- Artillery ---- Shelling ---- Shelling ---- Artillery ---- Unspecified Explosive ---- Firearms, Shelling ---- Shelling</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Secondary School ---- Not Applicable ---- University</t>
+          <t>Not Applicable ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- University ---- School: No Further Details ---- University ---- School: No Further Details ---- University ---- University ---- School: No Further Details ---- School: No Further Details</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr"/>
@@ -1830,64 +1679,64 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>South Darfur</t>
+          <t>North Darfur</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>SD03</t>
+          <t>SD02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Strategic developments ---- Strategic developments</t>
+          <t>Protests ---- Battles ---- Battles ---- Battles</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Disrupted weapons use ---- Looting/property destruction ---- Attack ---- Armed clash ---- Attack ---- Other ---- Change to group/activity</t>
+          <t>Peaceful protest ---- Armed clash ---- Armed clash ---- Armed clash</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Darfur Communal Militia (Sudan) ---- Military Forces of Sudan (2019-) ---- Darfur Communal Militia (Sudan) ---- Rapid Support Forces ---- Rapid Support Forces</t>
+          <t>Protesters (Sudan) ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-)</t>
+          <t>Refugees/IDPs (Sudan); Students (Sudan); Women (Sudan) ---- Darfur Arab Militia (Sudan) ---- Darfur Arab Militia (Sudan) ---- Darfur Arab Militia (Sudan)</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Civilians (Sudan) ---- Civilians (Sudan) ---- Civilians (Sudan) ---- Rapid Support Forces ---- Civilians (Sudan) ---- Civilians (Sudan)</t>
+          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-)</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Government of Sudan (2019-) ---- Students (Sudan); Teachers (Sudan) ---- Teachers (Sudan) ---- Teachers (Sudan) ---- Students (Sudan)</t>
+          <t>Darfur Joint Forces/JSAMF: Joint Force of Armed Struggle Movement ---- Darfur Joint Forces/JSAMF: Joint Force of Armed Struggle Movement</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>On 12 May 2024, RSF abducted the director of the Media Department at the Ministry of Education in Nyala (Nyala Janoub, South Darfur). No further information. ---- Defusal: On 8 August 2024, Baldna for Social Development Organization removed a landmine (planted during the clashes between SAF and RSF) in Jabal Marrah road, 6 RPG shells from Al-Khansa School, 6 120 mm mortar shells from the great market, and many unexploded ordnance from schools in Nyala (Nyala Janoub, South Darfur). ---- Looting: Around 24 August 2024 (as reported), RSF looted the faculties of Medicine and Health, University of Nyala in Nyala (Nyala Janoub, South Darfur). ---- Around 5 October 2024 (as reported), a militant (coded as Darfur communal militia) stabbed and killed a teacher in Nyala (Nyala Janoub, South Darfur). No further information. ---- On 14 October 2024, SAF airstrikes targeted RSF, while RSF responded with anti-aircraft fire in the airport and a market in Nyala (Nyala Janoub, South Darfur). Many civilians were killed and wounded. A school and civilians houses were destroyed in the east part of the city. Unspecified fatalities coded as 10. ---- On 6 December 2024, militants on motorbikes (coded as Darfur communal militia) shot and killed a teacher in his house in Nyala (Nyala Janoub, South Darfur), in an attempted looting. ---- Non-violent activity: On 25 December 2024, RSF imposed a curfew in Nyala (Nyala Janoub, South Darfur) and prevented students from traveling to SAF control area to set for the Sudanese certificate exams. ---- Recruitment: Around 8 June 2025 (as reported), RSF recruited an unspecified number of civilians, including minors and students, in Nyala (Nyala Janoub, South Darfur).</t>
+          <t>On 2 April 2024, Union school for girls IDPs-students staged a protest in El Fasher (Al Fasher, North Darfur), demanding water, food and sanitation. ---- On 18 June 2024, clashes between RSF, backed by allied militias (described as Arab militias, coded as Darfur Arab militia), and SAF, backed by Darfur Joint Forces/JSAMF, continued in north El Fasher (Al Fasher, North Darfur), with exchange artillery shelling being reported while SAF shelled a school which SAF claimed that RSF soldiers hid in. RSF advanced from the northern front into the city and were repelled by the Joint forces. SAF ordered civilians to evict their houses and deployed forces in Bernjia, Dadnga, Al Kifah, and Al Gadi neighborhoods. 4 - 15 civilians were killed and 19 were wounded. Civilians displacement continued. ---- On 3 September 2024, SAF airstrikes targeted RSF and inflected losses on them east El Fasher (Al Fasher, North Darfur), while RSF, backed by allied Arab militias (coded as Darfur Arab militia) shelled artillery targeting Al Radef, Tembasi, Al Riyad, and IDPs shelters in Al Ithad and Ibn Sena schools in El Fasher (Al Fasher, North Darfur). 2-4 civilians were killed and tens were wounded. Unspecified RSF fatalities coded as 10. Fatalities coded as 12 (2+10). ---- On 8 September 2024, clashes between RSF, backed by allied Arab militias (coded as Darfur Arab militia), and SAF, backed by Darfur Joint Forces/JSAMF, continued in south and east El Fasher (Al Fasher, North Darfur), with SAF airstrikes targeted RSF in north, east and south of the city additionally SAF and the Joint forces ground anti-aircraft fire shot down 30 RSF fighter drones which was reported includes C4. The Joint forces regained control over Al Manhal school. Casualties unknown.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>2024-05-12 ---- 2024-08-08 ---- 2024-08-24 ---- 2024-10-05 ---- 2024-10-14 ---- 2024-12-06 ---- 2024-12-25 ---- 2025-06-08</t>
+          <t>2024-04-02 ---- 2024-06-18 ---- 2024-09-03 ---- 2024-09-08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Nyala Janoub</t>
+          <t>Al Fasher</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -1897,154 +1746,92 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SD04122</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2024-08-25 ---- 2024-08-24</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">August 2024: A educator was shot and killed at his house by suspected Darfur communal militia.  ---- August 2024: A professor was killed inside his home by a group affiliated with the RSF. </t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Home ---- Home</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NSA ---- Vigilante</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Militia ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- Not Applicable</t>
-        </is>
-      </c>
+          <t>SD02124</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>West Darfur</t>
+          <t>North Darfur</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>SD04</t>
+          <t>SD02</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Air/drone strike</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Darfur Communal Militia (Sudan)</t>
+          <t>Military Forces of Sudan (2019-)</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>Civilians (Sudan)</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Teachers (Sudan)</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>On 25 August 2024, militants (coded as Darfur communal militia) shot and killed a teacher at his house in Gabi (location coded to Habila, West Darfur). No further information.</t>
+          <t>On 22 May 2024, SAF airstrikes targeted RSF in Kebkabiya (Kebkabiya, North Darfur). The airstrikes targeted Soleng school, Osman School Complex, Tabiya and Karkara neighborhoods. 4 to 16 civilians were killed and dozens were wounded. 9 houses were damaged.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Habila</t>
+          <t>Kebkabiya</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -2054,112 +1841,90 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SD04125</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">November 2024: A school was damaged by a SAF airstrike targeting RSF positions. </t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Sudanese Armed Forces</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>SD02128</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>North Darfur</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>SD02</t>
+        </is>
+      </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>On 6 February 2024, clashes between SAF and RSF continued in Al Zorg (Kutum, North Darfur), with SAF airstrikes and RSF shelling being reported. An unspecified number of houses, public facilities, and Quran schools were burned. 5 people were killed and 22 others were injured.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Kutum</t>
+        </is>
+      </c>
       <c r="AQ12" t="n">
         <v>0</v>
       </c>
@@ -2167,7 +1932,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SD07107</t>
+          <t>SD02129</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2201,13 +1966,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2223,12 +1988,12 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>March 2024: 11 students and two educators were killed and 45 people injured when a school was bombed by the SAF.</t>
+          <t>February 2025: An educational facility was damaged by an SAF airstrike.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2248,7 +2013,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Unspecified Explosive</t>
+          <t>Aerial Bomb: Plane</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2261,60 +2026,56 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>South Kordofan</t>
+          <t>North Darfur</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>SD07</t>
+          <t>SD02</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence</t>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Air/drone strike</t>
+          <t>Air/drone strike ---- Air/drone strike</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-)</t>
+          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-)</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Civilians (Sudan)</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Students (Sudan); Teachers (Sudan)</t>
-        </is>
-      </c>
+          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>On 14 March 2024, SAF airstrikes targeted a school in El Hadra (Delami, South Kordofan), El Kergil, Habila, and El Geniziaa Moro villages (coded separately). 13 to 14 people were killed, including 11 students and 2 teachers, and 45 were wounded. 100 families were displaced.</t>
+          <t>On 25 November 2024, SAF airstrikes targeted Koma (Al Fasher, North Darfur). 15 civilians were wounded. 19 houses and a school were damaged. ---- On 13 February 2025, SAF airstrikes targeted Koma (Al Fasher, North Darfur). A civilian was wounded. A school was damaged.</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-11-25 ---- 2025-02-13</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Delami</t>
+          <t>Melit</t>
         </is>
       </c>
       <c r="AQ13" t="n">
@@ -2324,116 +2085,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SD08106</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">April 2025: A professor was tortured after being arrested by military intelligence. He was forced to make a judicial confession before a local court judge. </t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Unspecified Location</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Police</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>General Intelligence Service (Sudan)</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>SD02171</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>North Darfur</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>SD02</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>On 23 January 2025, RSF abducted a student on the road to Port Sudan from Tina (At Tina, North Darfur).</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>At Tina</t>
+        </is>
+      </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
@@ -2441,158 +2180,88 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SD09050</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2025-02-07 ---- 2024-12-02 ---- 2024-03-01</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">February 2025: An educator was detained and then killed by the RSF. ---- As reported December 2024: An educator was killed by the RSF while taking students to register for exams. ---- March 2024: a university was hit and destroyed by SAF airstrikes, injuring an unspecified number. </t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public Building ---- Private Travel ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Vigilante ---- Vigilante ---- Other</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms ---- Aerial Bomb: Plane</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- Not Applicable ---- University</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Killed</t>
-        </is>
-      </c>
+          <t>SD03149</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>White Nile</t>
+          <t>South Darfur</t>
         </is>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>SD09</t>
+          <t>SD03</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Attack</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Students (Sudan) ---- Health Workers (Sudan)</t>
-        </is>
-      </c>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>On 16 December 2024, RSF abducted/detained students, searched their belongings, destroyed textbooks, and prevented them from crossing from Al Gitaina (Al Gitaina, White Nile) to Shaikh Seddig, to set for exams. ---- On 6 February 2025, RSF assaulted (means unspecified) residents and looted the Educational hospital, the pharmacy and destroyed medical equipment in Al Gitaina (Al Gitaina, White Nile). The RSF closed the hospital.</t>
+          <t>Other: On 12 December 2024, teachers announced the stop of teaching in Tullus (Tulus, South Darfur) and rejected RSF civic administration of replacement of the education director.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>2024-12-16 ---- 2025-02-06</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Al Gitaina</t>
+          <t>Tulus</t>
         </is>
       </c>
       <c r="AQ15" t="n">
@@ -2602,11 +2271,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SD12082</t>
+          <t>SD03161</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -2621,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2633,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2658,44 +2327,41 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2024: The director of a primary school was detained by members of the General Security Service. Whilst detained, they were kicked, slapped, and whipped and their hair shaved. </t>
+          <t xml:space="preserve">February 2024: a secondary school was looted and destroyed by the RSF. 170 chairs, 150 stairs steps, 30 educators‚Äô desks, ten cupboards, two large water pipes, a car, doors, windows, roof material and a laboratory were taken._x000D_
+</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Unspecified Location</t>
+          <t xml:space="preserve">Education Building </t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Vigilante</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>National Intelligence and Security Services (Sudan)</t>
+          <t>Rapid Support Forces</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Fist and Foot</t>
+          <t>Firearms</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2719,11 +2385,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SD13023</t>
+          <t>SD03167</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -2735,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2753,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2771,41 +2437,41 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2024-12-17 ---- 2024-10-05 ---- 2024-08-24</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>January 2024: University vandalised by the RSF.</t>
+          <t xml:space="preserve">December 2024: An education facility sheltering IDPs was hit by SAF airstrikes, killing nine people and injuring at least 15 other including children.  ---- October 2024: An educator was stabbed and killed by an unidentified militia. ---- As reported in August 2024: The faculties of Medicine and Health at a university were looted by the RSF. </t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building </t>
+          <t xml:space="preserve">Education Building  ---- Unspecified Location ---- Education Building </t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Vigilante</t>
+          <t>Other ---- NSA ---- Vigilante</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Rapid Support Forces</t>
+          <t>Sudanese Armed Forces ---- Militia ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>No Information on the Weapon Used</t>
+          <t>Aerial Bomb: Plane ---- Knife ---- No Information on the Weapon Used</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Secondary School ---- Not Applicable ---- University</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
@@ -2813,64 +2479,64 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>North Kordofan</t>
+          <t>South Darfur</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>SD13</t>
+          <t>SD03</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Battles ---- Violence against civilians ---- Explosions/Remote violence</t>
+          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Strategic developments ---- Strategic developments</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Armed clash ---- Attack ---- Remote explosive/landmine/IED</t>
+          <t>Abduction/forced disappearance ---- Disrupted weapons use ---- Looting/property destruction ---- Attack ---- Armed clash ---- Attack ---- Other ---- Change to group/activity</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Military Forces of Sudan (2019-) ---- Unidentified Armed Group (Sudan)</t>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Darfur Communal Militia (Sudan) ---- Military Forces of Sudan (2019-) ---- Darfur Communal Militia (Sudan) ---- Rapid Support Forces ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Al Baraa Ibn Malik Brigade</t>
+          <t>Military Forces of Sudan (2019-)</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-) ---- Civilians (Sudan) ---- Civilians (Sudan)</t>
+          <t>Civilians (Sudan) ---- Civilians (Sudan) ---- Civilians (Sudan) ---- Rapid Support Forces ---- Civilians (Sudan) ---- Civilians (Sudan)</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Government of Sudan (2019-); NUP: National Umma Party; Rapid Support Forces; Teachers (Sudan) ---- Students (Sudan)</t>
+          <t>Government of Sudan (2019-) ---- Students (Sudan); Teachers (Sudan) ---- Teachers (Sudan) ---- Teachers (Sudan) ---- Students (Sudan)</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>On 21 January 2025, 5 RSF fighter drones targeted SAF while SAF responded with ground anti-aircraft fire in Al Ghabsha (Um Rawaba, North Kordofan). SAF shot down 4 RSF fighter drones. A school was damaged. There were no casualties. ---- On 31 January 2025, SAF, supported by Al Baraa Ibn Malik, killed an unspecified number of civilians, beheaded the NUP locality's Chairman and the locality director of education, and arrested others in Umm Rawaba (Um Rawaba, North Kordofan), accusing them of collaborating with RSF. Unspecified fatalities coded 10. ---- On 28 May 2025, a shell planted by an unspecified armed group (coded as unidentified armed group) exploded when a student brought it to a school in Al Ghabsha (Um Rawaba, North Kordofan). 4 - 5 students were killed and 9 were wounded.</t>
+          <t>On 12 May 2024, RSF abducted the director of the Media Department at the Ministry of Education in Nyala (Nyala Janoub, South Darfur). No further information. ---- Defusal: On 8 August 2024, Baldna for Social Development Organization removed a landmine (planted during the clashes between SAF and RSF) in Jabal Marrah road, 6 RPG shells from Al-Khansa School, 6 120 mm mortar shells from the great market, and many unexploded ordnance from schools in Nyala (Nyala Janoub, South Darfur). ---- Looting: Around 24 August 2024 (as reported), RSF looted the faculties of Medicine and Health, University of Nyala in Nyala (Nyala Janoub, South Darfur). ---- Around 5 October 2024 (as reported), a militant (coded as Darfur communal militia) stabbed and killed a teacher in Nyala (Nyala Janoub, South Darfur). No further information. ---- On 14 October 2024, SAF airstrikes targeted RSF, while RSF responded with anti-aircraft fire in the airport and a market in Nyala (Nyala Janoub, South Darfur). Many civilians were killed and wounded. A school and civilians houses were destroyed in the east part of the city. Unspecified fatalities coded as 10. ---- On 6 December 2024, militants on motorbikes (coded as Darfur communal militia) shot and killed a teacher in his house in Nyala (Nyala Janoub, South Darfur), in an attempted looting. ---- Non-violent activity: On 25 December 2024, RSF imposed a curfew in Nyala (Nyala Janoub, South Darfur) and prevented students from traveling to SAF control area to set for the Sudanese certificate exams. ---- Recruitment: Around 8 June 2025 (as reported), RSF recruited an unspecified number of civilians, including minors and students, in Nyala (Nyala Janoub, South Darfur).</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>2025-01-21 ---- 2025-01-31 ---- 2025-05-28</t>
+          <t>2024-05-12 ---- 2024-08-08 ---- 2024-08-24 ---- 2024-10-05 ---- 2024-10-14 ---- 2024-12-06 ---- 2024-12-25 ---- 2025-06-08</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Um Rawaba</t>
+          <t>Nyala Janoub</t>
         </is>
       </c>
       <c r="AQ17" t="n">
@@ -2880,162 +2546,92 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SD13024</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>27</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2025-03-13 ---- 2025-02-08 ---- 2025-01-30 ---- 2024-08-26 ---- 2024-08-14</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">March 2025: Laboratories in a medical education facility were destroyed due to artillery shelling by the RSF.  ---- February 2025: An education facility was damaged and an unspecified number of people were injured and killed by RSF artillery. ---- January 2025: An educator was killed by the SAF. He was the director of an education facility and one of the leaders of the a political party. ---- August 2024: A lecturer who works at various Sudanese universities was arrested by the RSF who took him to an unknown location. He was stopped with other passengers on a commercial bus. ---- August 2024:A secondary school was hit with RSF shells, killing five girls and injuring 20 children. </t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public Building ---- Education Building  ---- Unspecified Location ---- Private Travel ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Vigilante ---- Vigilante ---- Other ---- Vigilante ---- Vigilante</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Artillery ---- Artillery ---- Firearms ---- Firearms ---- Shelling</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>University ---- School: No Further Details ---- Not Applicable ---- Not Applicable ---- Secondary School</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>SD04121</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>North Kordofan</t>
+          <t>West Darfur</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>SD13</t>
+          <t>SD04</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Battles ---- Strategic developments ---- Violence against civilians</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Armed clash ---- Other ---- Attack</t>
+          <t>Looting/property destruction</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-) ---- Protesters (Sudan) ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Health Workers (Sudan)</t>
-        </is>
-      </c>
+          <t>Darfur Communal Militia (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Rapid Support Forces ---- Civilians (Sudan)</t>
+          <t>Civilians (Sudan)</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Students (Sudan)</t>
+          <t>Labor Group (Sudan)</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>On 14 August 2024, RSF shelled artillery targeting multiple areas, including two schools, while SAF responded with artillery shelling targeting RSF positions in El Obeid (Sheikan, North Kordofan). 4-20 civilians were killed and 40-125 were wounded, including 30 students. Fatalities coded as 4. ---- Strikes: Around 6 November 2024 (as reported), doctors of El Obeid Educational hospital launched a strike in El Obeid (Sheikan, North Kordofan), demanding salaries. ---- On 29 December 2024, RSF shot and killed a student and his father in El Obeid (Sheikan, North Darfur), while the student was trying to travel to take high school exams.</t>
+          <t>Looting: Around 21 November 2024 (as reported), militants (coded as Darfur communal militia) looted employees of Ministry of Education in West Darfur State in Jabal Kajing in the road between Bida and Foro Burunga (Foro Baranga, West Darfur).</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>2024-08-14 ---- 2024-11-06 ---- 2024-12-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Sheikan</t>
+          <t>Foro Baranga</t>
         </is>
       </c>
       <c r="AQ18" t="n">
@@ -3045,14 +2641,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SD14038</t>
+          <t>SD04122</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3064,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3097,41 +2693,41 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-08-25 ---- 2024-08-24</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>December 2024: A university was damaged by the RSF.</t>
+          <t xml:space="preserve">August 2024: A educator was shot and killed at his house by suspected Darfur communal militia.  ---- August 2024: A professor was killed inside his home by a group affiliated with the RSF. </t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building </t>
+          <t>Home ---- Home</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Vigilante</t>
+          <t>NSA ---- Vigilante</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Rapid Support Forces</t>
+          <t>Militia ---- Rapid Support Forces</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Firearms</t>
+          <t>Firearms ---- Firearms</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Not Applicable ---- Not Applicable</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr"/>
@@ -3139,7 +2735,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sennar</t>
+          <t>West Darfur</t>
         </is>
       </c>
       <c r="AD19" t="n">
@@ -3150,7 +2746,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>SD14</t>
+          <t>SD04</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
@@ -3166,7 +2762,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-)</t>
+          <t>Darfur Communal Militia (Sudan)</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr"/>
@@ -3175,20 +2771,24 @@
           <t>Civilians (Sudan)</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Around 5 January 2025 (as reported), SAF gunfire targeted a civilian driving off shot in Sennar (Sennar, Sennar) after a road accident between SAF and the civilian. A high school student was killed.</t>
+          <t>On 25 August 2024, militants (coded as Darfur communal militia) shot and killed a teacher at his house in Gabi (location coded to Habila, West Darfur). No further information.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Sennar</t>
+          <t>Habila</t>
         </is>
       </c>
       <c r="AQ19" t="n">
@@ -3198,14 +2798,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SD14039</t>
+          <t>SD04125</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3254,13 +2854,12 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">As reported in July 2024: A university college was attacked and destroyed during an attack on the village by the RSF._x000D_
-</t>
+          <t xml:space="preserve">November 2024: A school was damaged by a SAF airstrike targeting RSF positions. </t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3270,22 +2869,22 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Vigilante</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Rapid Support Forces</t>
+          <t>Sudanese Armed Forces</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Unspecified Explosive</t>
+          <t>Aerial Bomb: Plane</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>School: No Further Details</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr"/>
@@ -3312,112 +2911,94 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SD14043</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As reported in July 2024: A professor was killed inside their home during an attack on the city by the RSF. </t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Vigilante</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+          <t>SD05142</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>East Darfur</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>SD05</t>
+        </is>
+      </c>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Air/drone strike ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-) ---- Military Forces of Sudan (2019-) ---- Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>On 20 August 2024, SAF airstrikes targeted Educational hospital and the market in Ed Daein (Ad Duayn, East Darfur). The hospital was destroyed and went out of service. 18 civilians were killed and 21 were wounded. ---- On 21 August 2024, SAF airstrikes targeted Educational hospital and other locations in Ed Daein (Ad Duayn, East Darfur). Casualties unknown. ---- On 31 March 2025, RSF abducted a teacher in Ed Daein (Ad Duayn, East Darfur). No further information.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>2024-08-20 ---- 2024-08-21 ---- 2025-03-31</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>Ad Duayn</t>
+        </is>
+      </c>
       <c r="AQ21" t="n">
         <v>0</v>
       </c>
@@ -3425,101 +3006,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SD15031</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2025-01-23 ---- 2025-01-17 ---- 2024-07-23 ---- 2024-05-12 ---- 2024-01-13 ---- 2024-01-03</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">January 2025: An education facility had a shell fall into its courtyard when the nearby airport was shelled by RSF. ---- January 2025: The library of the Faculty of Medicine at an education facility was damaged and looted by the RSF. ---- July 2024: Medical equipment was looted and the faculties of medicine and laboratories vandalised at a university, by the RSF. ---- May 2024: A university was attacked by the RSF. ---- January 2024: College complex bombed by the SAF.  ---- January 2024: All campuses of a university were looted by the RSF, including the administration offices, the university‚Äôs saving bank, its farm and the International Hall. Additionally, the professors‚Äô houses, in the surrounding neighbourhoods, were also attacked. </t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Other ---- Vigilante</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Shelling ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Aerial Bomb: Plane ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>University ---- University ---- University ---- University ---- Secondary School ---- University</t>
-        </is>
-      </c>
+          <t>SD05160</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Al Jazirah</t>
+          <t>East Darfur</t>
         </is>
       </c>
       <c r="AD22" t="n">
@@ -3530,23 +3049,23 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>SD15</t>
+          <t>SD05</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Air/drone strike</t>
+          <t>Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>Military Forces of Sudan (2019-)</t>
+          <t>Rapid Support Forces</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr"/>
@@ -3555,20 +3074,24 @@
           <t>Civilians (Sudan)</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-); Teachers (Sudan)</t>
+        </is>
+      </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>On 23 January 2024, SAF airstrikes targeted the area near Beka bridge and a school compound in Beka (Janub Al Jazirah, Al Jazirah). 0-1 civilians were killed and 1 was injured.</t>
+          <t>On 20 June 2025, RSF abducted the Education Director of Secondary Schools in Abu Matariq (Bahr Al Arab, East Darfur), after accusing him of collaborating with SAF.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>Janub Al Jazirah</t>
+          <t>Bahr Al Arab</t>
         </is>
       </c>
       <c r="AQ22" t="n">
@@ -3578,107 +3101,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SD15034</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>2024-09-06 ---- 2024-07-07 ---- 2024-05-11 ---- 2024-05-02 ---- 2024-01-10 ---- 2024-01-04</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">September 2024: A teacher was shot and killed inside her home by the RSF after she resisted their attempt at sexual assault in front of her husband and children. She died the next day.  ---- July 2024: Two educators were killed by an armed force affiliated with the RSF. _x000D_
- ---- May 2024: A university employee was killed by the RSF who stormed his house.  ---- May 2024: A professor was shot in the stomach by the RSF after they stopped two of their relatives. They died two days later.  ---- January 2024: Professor arrested and killed by the RSF. _x000D_
- ---- January 2024: University stormed by the RSF. </t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Home ---- Unspecified Location ---- Home ---- Unspecified Location ---- Unspecified Location ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Firearms ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- Not Applicable ---- Not Applicable ---- Not Applicable ---- Not Applicable ---- University</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Killed</t>
-        </is>
-      </c>
+          <t>SD06138</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Al Jazirah</t>
+          <t>Central Darfur</t>
         </is>
       </c>
       <c r="AD23" t="n">
@@ -3689,18 +3144,18 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>SD15</t>
+          <t>SD06</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3716,22 +3171,22 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Teachers (Sudan)</t>
+          <t>Students (Sudan)</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>On 18 January 2025, RSF abducted a professor from his house in El Hasahisa (Al Hasahisa, Al Jazirah) for ransom.</t>
+          <t>Non-violent activity: On 8 December 2024, RSF civic administration announced their refusal of Sudanese certificate exams in parts of country and in Central Darfur RSF prevented students from travelling to SAF controlled areas in White Nile, and River Nile states to sit for the Sudanese certificate exams in Zalingei (Zalingi, Central Darfur).</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>Al Hasahisa</t>
+          <t>Zalingi</t>
         </is>
       </c>
       <c r="AQ23" t="n">
@@ -3741,112 +3196,94 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SD17018</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>October 2024: A student travelling to an exam was detained by the SAF. The student was sentenced to five years in prison for cooperating with the RSF. The family demanded his release and the cancellation of the judicial ruling.</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Private Travel</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Sudanese Armed Forces</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Secondary School</t>
-        </is>
-      </c>
+          <t>SD07094</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>South Kordofan</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>SD07</t>
+        </is>
+      </c>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Around 25 February 2025 (as reported), RSF tortured and killed (through unspecified means) a teacher in Dibebad (Al Quoz, South Kordofan). No further information.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Al Quoz</t>
+        </is>
+      </c>
       <c r="AQ24" t="n">
         <v>0</v>
       </c>
@@ -3854,101 +3291,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SD18022</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>May 2025: An educator/head of programme, and his son, were killed by the RSF in their home.</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Vigilante</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Rapid Support Forces</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+          <t>SD07095</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>West Kordofan</t>
+          <t>South Kordofan</t>
         </is>
       </c>
       <c r="AD25" t="n">
@@ -3959,52 +3334,3578 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>SD18</t>
+          <t>SD07</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>On 27 December 2024, tens of students staged a protest in Dilling (Dilling, South Kordofan), denouncing the delay of receiving exams papers in the exam centers.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Dilling</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SD07096</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>South Kordofan</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>SD07</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan) ---- Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>On 21 March 2024, students in Nuba Mountains staged a protest in Kauda (Heiban, South Kordofan), denouncing SAF airstrikes on El Hadra school (coded separately). ---- On 28 March 2024, residents demonstrated in Kauda (Heiban, South Kordofan), denouncing a school targeting by SAF airstrikes in Hidra (coded separately).</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>2024-03-21 ---- 2024-03-28</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Heiban</t>
+        </is>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SD07098</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>South Kordofan</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>SD07</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Non-violent activity: Around 28 November 2024 (from 28 - 29 November), the security committee (SAF) evicted (through unspecified means) IDPs from schools in Kadugli (Kadugli, South Kordofan).</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>Kadugli</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SD07107</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>58</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>40</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>March 2024: 11 students and two educators were killed and 45 people injured when a school was bombed by the SAF.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sudanese Armed Forces</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Unspecified Explosive</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>South Kordofan</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>SD07</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Students (Sudan); Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>On 14 March 2024, SAF airstrikes targeted a school in El Hadra (Delami, South Kordofan), El Kergil, Habila, and El Geniziaa Moro villages (coded separately). 13 to 14 people were killed, including 11 students and 2 teachers, and 45 were wounded. 100 families were displaced.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>Delami</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SD08105</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Blue Nile</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>SD08</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
+        <is>
           <t>Violence against civilians</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>STC: Sudanese Teachers' Committee; Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Around 22 April 2025 (as reported), SAF arrested and 'tortured' an STC member in Ed Damazin (Ed Damazine, Blue Nile).</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Ed Damazine</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SD08106</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April 2025: A professor was tortured after being arrested by military intelligence. He was forced to make a judicial confession before a local court judge. </t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>General Intelligence Service (Sudan)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SD09050</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2025-02-07 ---- 2024-12-02 ---- 2024-03-01</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">February 2025: An educator was detained and then killed by the RSF. ---- As reported December 2024: An educator was killed by the RSF while taking students to register for exams. ---- March 2024: a university was hit and destroyed by SAF airstrikes, injuring an unspecified number. </t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public Building ---- Private Travel ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Vigilante ---- Vigilante ---- Other</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms ---- Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Not Applicable ---- University</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Killed</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>White Nile</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>SD09</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Attack</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Students (Sudan) ---- Health Workers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>On 16 December 2024, RSF abducted/detained students, searched their belongings, destroyed textbooks, and prevented them from crossing from Al Gitaina (Al Gitaina, White Nile) to Shaikh Seddig, to set for exams. ---- On 6 February 2025, RSF assaulted (means unspecified) residents and looted the Educational hospital, the pharmacy and destroyed medical equipment in Al Gitaina (Al Gitaina, White Nile). The RSF closed the hospital.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>2024-12-16 ---- 2025-02-06</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Al Gitaina</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SD10064</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Red Sea</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>SD10</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>On 5 November 2024, tens of students staged a protest in front of Egypt embassy in Port Sudan (Port Sudan, Red Sea), demanding the issuing of their entry visa to Egypt to join the universities there.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SD11053</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Kassala</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>SD11</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>Strikes: On 13 January 2025, teachers launched a strike across Kassala state (location coded to state capital in Kassala, Madeinat Kassala), demanding their salaries.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Madeinat Kassala</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SD12080</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gedaref</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>SD12</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>Rapid Support Forces</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr">
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>On 9 April 2024, suspected RSF conducted a drone strike targeting the General Intelligence Service HQ in Gedaref (Madeinat Al Gedaref, Gedaref), while SAF shot down 2 drones attempting to target the SAF National Service center and a school. 3 civilians were injured.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>Madeinat Al Gedaref</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SD12082</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">May 2024: The director of a primary school was detained by members of the General Security Service. Whilst detained, they were kicked, slapped, and whipped and their hair shaved. </t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>National Intelligence and Security Services (Sudan)</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Fist and Foot</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SD12084</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gedaref</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>SD12</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr">
         <is>
           <t>Civilians (Sudan)</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Labor Group (Sudan); Prisoners (Sudan); Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Around 29 April 2024 (as reported), SAF tortured 5 civilians (including a teacher and 2 workers) in El Hawata prison in El Hawata (Ar Rahad, Gedaref) after detaining them on 29 April due to their anti-war social media posts. They were released on 30 April. No information on injuries.</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Ar Rahad</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SD13023</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>January 2024: University vandalised by the RSF.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Vigilante</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>North Kordofan</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>SD13</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Battles ---- Violence against civilians ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Attack ---- Remote explosive/landmine/IED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Military Forces of Sudan (2019-) ---- Unidentified Armed Group (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Al Baraa Ibn Malik Brigade</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-) ---- Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Government of Sudan (2019-); NUP: National Umma Party; Rapid Support Forces; Teachers (Sudan) ---- Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>On 21 January 2025, 5 RSF fighter drones targeted SAF while SAF responded with ground anti-aircraft fire in Al Ghabsha (Um Rawaba, North Kordofan). SAF shot down 4 RSF fighter drones. A school was damaged. There were no casualties. ---- On 31 January 2025, SAF, supported by Al Baraa Ibn Malik, killed an unspecified number of civilians, beheaded the NUP locality's Chairman and the locality director of education, and arrested others in Umm Rawaba (Um Rawaba, North Kordofan), accusing them of collaborating with RSF. Unspecified fatalities coded 10. ---- On 28 May 2025, a shell planted by an unspecified armed group (coded as unidentified armed group) exploded when a student brought it to a school in Al Ghabsha (Um Rawaba, North Kordofan). 4 - 5 students were killed and 9 were wounded.</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>2025-01-21 ---- 2025-01-31 ---- 2025-05-28</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Um Rawaba</t>
+        </is>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SD13024</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>27</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>20</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2025-03-13 ---- 2025-02-08 ---- 2025-01-30 ---- 2024-08-26 ---- 2024-08-14</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">March 2025: Laboratories in a medical education facility were destroyed due to artillery shelling by the RSF.  ---- February 2025: An education facility was damaged and an unspecified number of people were injured and killed by RSF artillery. ---- January 2025: An educator was killed by the SAF. He was the director of an education facility and one of the leaders of the a political party. ---- August 2024: A lecturer who works at various Sudanese universities was arrested by the RSF who took him to an unknown location. He was stopped with other passengers on a commercial bus. ---- August 2024:A secondary school was hit with RSF shells, killing five girls and injuring 20 children. </t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public Building ---- Education Building  ---- Unspecified Location ---- Private Travel ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Vigilante ---- Vigilante ---- Other ---- Vigilante ---- Vigilante</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Artillery ---- Artillery ---- Firearms ---- Firearms ---- Shelling</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>University ---- School: No Further Details ---- Not Applicable ---- Not Applicable ---- Secondary School</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>North Kordofan</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>SD13</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Battles ---- Strategic developments ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Other ---- Attack</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-) ---- Protesters (Sudan) ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
         <is>
           <t>Health Workers (Sudan)</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>On 14 August 2024, RSF shelled artillery targeting multiple areas, including two schools, while SAF responded with artillery shelling targeting RSF positions in El Obeid (Sheikan, North Kordofan). 4-20 civilians were killed and 40-125 were wounded, including 30 students. Fatalities coded as 4. ---- Strikes: Around 6 November 2024 (as reported), doctors of El Obeid Educational hospital launched a strike in El Obeid (Sheikan, North Kordofan), demanding salaries. ---- On 29 December 2024, RSF shot and killed a student and his father in El Obeid (Sheikan, North Darfur), while the student was trying to travel to take high school exams.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>2024-08-14 ---- 2024-11-06 ---- 2024-12-29</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Sheikan</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SD13026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>North Kordofan</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>SD13</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Students (Sudan); Sufi Muslim Group (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Land seizure: Around 15 June 2025 (month of), RSF overtook Sufi school mosque (Khalwa) Kharsi (Bara, North Kordofan), and displaced the students.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Bara</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SD13028</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>North Kordofan</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>SD13</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>Around 17 February 2025 (as reported), RSF chased a vehicle carrying teachers heading to SAF-controlled areas, in Al Zariba (Um Dam Haj Ahmed, North Kordofan). 1 teacher broke his leg.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>Um Dam Haj Ahmed</t>
+        </is>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SD14038</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>December 2024: A university was damaged by the RSF.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Vigilante</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sennar</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>SD14</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>Around 5 January 2025 (as reported), SAF gunfire targeted a civilian driving off shot in Sennar (Sennar, Sennar) after a road accident between SAF and the civilian. A high school student was killed.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Sennar</t>
+        </is>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SD14039</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As reported in July 2024: A university college was attacked and destroyed during an attack on the village by the RSF._x000D_
+</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Vigilante</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Unspecified Explosive</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SD14043</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As reported in July 2024: A professor was killed inside their home during an attack on the city by the RSF. </t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Vigilante</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SD15030</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Violence against civilians ---- Explosions/Remote violence ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Looting/property destruction ---- Abduction/forced disappearance ---- Remote explosive/landmine/IED ---- Other</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Unidentified Armed Group (Sudan) ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan) ---- Civilians (Sudan) ---- Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Labor Group (Sudan); Students (Sudan); Teachers (Sudan) ---- Military Forces of Sudan (2019-); Students (Sudan); Teachers (Sudan) ---- Students (Sudan) ---- Military Forces of Sudan (2019-); Students (Sudan); Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>Looting: Around 2 January 2024 (as reported), RSF looted Al Jazira University in Wad Medani (Medani Al Kubra, Al Jazirah), including the on-campus bank and student and lecturer residences. ---- On 12 December 2024, RSF abducted 5 teachers and 5 students around Wad Medani (Medani Al Kubra, Al Jazirah) while the students were on their way to El Managil to take the national high school exit exams, accusing them of providing intelligence to SAF. The 10 students and teachers were found buried in a mass grave in Wad Medani on 3 June 2025 (coded separately) after being tortured by RSF. ---- Around 14 May 2025 (as reported), a DShK round fired by an unspecified group (coded as unidentified armed group) exploded in a classroom in Jabr (Medani Al Kubra, Al Jazirah) after a student discovered the round and began handling it. 1 child was killed and 3 others were injured. ---- Mass grave: On 3 June 2025, police forces discovered 2 mass graves containing 10-12 bodies of teachers and students tortured by RSF and buried by civilians in Al Zamalek cinema in Wad Medani (Medani Al Kubra, Al Jazirah) after RSF abducted them on their way to El Managil to sit for high school exit exams (coded separately) on suspicion of providing intelligence to SAF.</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>2024-01-02 ---- 2024-12-12 ---- 2025-05-14 ---- 2025-06-03</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>Medani Al Kubra</t>
+        </is>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SD15031</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2025-01-23 ---- 2025-01-17 ---- 2024-07-23 ---- 2024-05-12 ---- 2024-01-13 ---- 2024-01-03</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">January 2025: An education facility had a shell fall into its courtyard when the nearby airport was shelled by RSF. ---- January 2025: The library of the Faculty of Medicine at an education facility was damaged and looted by the RSF. ---- July 2024: Medical equipment was looted and the faculties of medicine and laboratories vandalised at a university, by the RSF. ---- May 2024: A university was attacked by the RSF. ---- January 2024: College complex bombed by the SAF.  ---- January 2024: All campuses of a university were looted by the RSF, including the administration offices, the university‚Äôs saving bank, its farm and the International Hall. Additionally, the professors‚Äô houses, in the surrounding neighbourhoods, were also attacked. </t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Other ---- Vigilante</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Sudanese Armed Forces ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Shelling ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Aerial Bomb: Plane ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>University ---- University ---- University ---- University ---- Secondary School ---- University</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>On 23 January 2024, SAF airstrikes targeted the area near Beka bridge and a school compound in Beka (Janub Al Jazirah, Al Jazirah). 0-1 civilians were killed and 1 was injured.</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>Janub Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SD15033</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>On 15 November 2024, RSF abducted 5 civilians in Rufaah (Sharg Al Jazirah, Al Jazirah), including a retired teacher, for ransom.</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>Sharg Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SD15034</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2024-09-06 ---- 2024-07-07 ---- 2024-05-11 ---- 2024-05-02 ---- 2024-01-10 ---- 2024-01-04</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">September 2024: A teacher was shot and killed inside her home by the RSF after she resisted their attempt at sexual assault in front of her husband and children. She died the next day.  ---- July 2024: Two educators were killed by an armed force affiliated with the RSF. _x000D_
+ ---- May 2024: A university employee was killed by the RSF who stormed his house.  ---- May 2024: A professor was shot in the stomach by the RSF after they stopped two of their relatives. They died two days later.  ---- January 2024: Professor arrested and killed by the RSF. _x000D_
+ ---- January 2024: University stormed by the RSF. </t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home ---- Unspecified Location ---- Home ---- Unspecified Location ---- Unspecified Location ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante ---- Vigilante</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Firearms ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Not Applicable ---- Not Applicable ---- Not Applicable ---- Not Applicable ---- University</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Killed</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>On 18 January 2025, RSF abducted a professor from his house in El Hasahisa (Al Hasahisa, Al Jazirah) for ransom.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>Al Hasahisa</t>
+        </is>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SD15035</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Riots</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Attack ---- Mob violence</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces ---- Rioters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan) ---- Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Teachers (Sudan) ---- Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>On 6 September 2024, RSF shot a teacher inside her house in Al Masid (Al Kamlin, Al Jazirah) after she resisted their attempt at sexual assault. She died the next day. ---- On 4 August 2025, residents of Um Magad village attacked children from their neighboring Kambo Al Azazah (a settlement housing migrant workers from western and southern Sudan), using sticks and stones, while they were returning from school on the Khartoum-Medani national road (location coded to Um Magad, Al Kamlin, Al Jazirah) and shouted xenophobic insults targeting them. 3 students were injured, and another was critically wounded.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>2024-09-06 ---- 2025-08-04</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>Al Kamlin</t>
+        </is>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SD15036</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Al Jazirah</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>SD15</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Sudan) ---- Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Health Workers (Sudan); Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>On 27 February 2024, an armed group (coded as unidentified armed group) shot and killed a medical student in Al Kiremit (Al Manaqil, Al Jazirah) for unspecified reasons. ---- Around 31 January 2025 (as reported), residents protested in Kambo (settlement housing migrant workers from western and southern Sudan) 80 near Al Kiremit (Al Manaqil, Al Jazirah) against a decision to build a fuel station on contested land the residents planned on using for building a school.</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>2024-02-27 ---- 2025-01-31</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>Al Manaqil</t>
+        </is>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SD16010</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>River Nile</t>
+        </is>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>SD16</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Sudanese Popular Resistance Factions</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Students (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Around 16 August 2024 (as reported), a Sudanese Popular Resistance Factions member killed a student in Shendi (Shendi, River Nile). Motivation unknown/not reported.</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>Shendi</t>
+        </is>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SD16012</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>River Nile</t>
+        </is>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>SD16</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Violence against civilians ---- Battles</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Looting/property destruction ---- Attack ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Police Forces of Sudan (2019-) ---- Police Forces of Sudan (2019-) ---- Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan) ---- Civilians (Sudan) ---- Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Sudan) ---- Refugees/IDPs (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Property destruction: On 29 April 2024, police forces destroyed IDP's belongings in a school used as an IDP center in Atbara (Atbara, River Nile) to evict them so it could be used as an examination center. Two people were arrested for not wanting to leave. ---- On 2 May 2024, security forces (likely police forces due to a similar raid by police on April 29) assaulted and injured IDPs in a dormitory IDP center in Atbara (Atbara, River Nile) and destroyed their belongings to forcefully evict them and replace them with students. ---- On 11 January 2025, RSF fighter drones targeted SAF, while SAF responded with anti-aircraft fire in Atbara (Atbara, River Nile). There were no casualties. A school was damaged.</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>2024-04-29 ---- 2024-05-02 ---- 2025-01-11</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>Atbara</t>
+        </is>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SD17018</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>October 2024: A student travelling to an exam was detained by the SAF. The student was sentenced to five years in prison for cooperating with the RSF. The family demanded his release and the cancellation of the judicial ruling.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Private Travel</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sudanese Armed Forces</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SD17020</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Northern</t>
+        </is>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>SD17</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan)</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Students (Sudan); Teachers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>On 6 August 2025, tens of students and teachers staged a protest in Karima (Merowe, Northern), denouncing the power outages.</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>Merowe</t>
+        </is>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SD18022</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>May 2025: An educator/head of programme, and his son, were killed by the RSF in their home.</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Vigilante</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>West Kordofan</t>
+        </is>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>SD18</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Civilians (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Health Workers (Sudan)</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Around 14 July 2025 (as reported), RSF beat civilians in Suliman Center, Educational, and Al Bashir hospitals in An Nahud (An Nuhud, West Kordofan) after some of them refused to be forcibly expelled so that RSF could use the hospital to treat their wounded. Extent of injuries unknown/not reported.</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AP54" t="inlineStr">
         <is>
           <t>An Nuhud</t>
         </is>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SD18100</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>West Kordofan</t>
+        </is>
+      </c>
+      <c r="AD55" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>SD18</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Rapid Support Forces</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Military Forces of Sudan (2019-)</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>On 24 January 2024, clashes between RSF and SAF continued in Al Salam, Bashma, University Education, Abu Ismail, Babanusa Dairy Factory neighborhoods, in addition to the railway headquarters and Babanusa market in Babanussa (Babanusa, West Kordofan), with SAF airstrikes on Babanussa Dairy factory and artillery shelling being reported. SAF repelled RSF attack. RSF looted the market, the local police headquarters, the railway headquarters, and several government facilities. RSF overrun some SAF defensive positions. Huge civilian displacement was reported. SAF destroyed 33 RSF vehicles. 45 RSF soldiers were killed (reported only by one source), and dozens wounded. 16 civilians were killed and 18 were wounded. At least 23 civilians were killed, 30 were wounded and 6 were abducted between 22-24 of January. 5 unspecified fatalities (23 minus 2 civilians killed on the 23rd and 16 civilians killed on the 24th) split over three days, coded as 1 for this event. Fatalities coded as 62 (45 RSF + 17 civilians).</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Babanusa</t>
+        </is>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SD19001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Abyei</t>
+        </is>
+      </c>
+      <c r="AD56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>SD19</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Protests ---- Battles</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Protesters (Sudan) ---- Bul Clan Militia (South Sudan)</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Ngok Clan Group (Sudan); Dinka Ethnic Group (Sudan); Government of Sudan (2019-); Students (Sudan) ---- Nuer Ethnic Militia (South Sudan); Pastoralists (South Sudan)</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Unidentified Communal Militia (Sudan)</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Pastoralists (South Sudan)</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>On 19 April 2024, between 500 - 700 members of the Ngok Dinka community, including civil society actors, local leaders, government officials and students, held a peaceful protest in Abyei Town (Abyei disputed area), over a range of issues. The group marched to the United Nations Interim Security Force for Abyei (UNISFA) compound to present a petition to the UNISFA representative. ---- On 27 July 2025, unidentified armed youth suspected to be from Unity State's Mayom County (likely members of the Bul Nuer community, which is predominant in the area) clashed with local youth (coded as unidentified communal militia) when the former raided an unspecified number of cattle in Ameth-bek village, Rumameer Payam, Abyei County (Abyei disputed area), resulting in 5 fatalities, including a teacher, and 5 injuries. Local youth recovered the stolen animals.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>2024-04-19 ---- 2025-07-27</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>Abyei</t>
+        </is>
+      </c>
+      <c r="AQ56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4275,13 +7176,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7093E98-99BA-4B6F-BC39-14548AFAE578}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E07BFC1B-9D64-48FF-ADC1-17B5C71E1309}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FC47CDD-5F2C-4655-A3B1-15179C17F467}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B38C7ED8-950F-4886-BF8D-4877CE2277AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14015DD3-2887-4CCC-834A-BAB07B70F6DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DFA28BE-81CD-44C6-80CC-A97DB855ED92}"/>
 </file>